--- a/results/Int All Data 0.7/Rando_10_permute.xlsx
+++ b/results/Int All Data 0.7/Rando_10_permute.xlsx
@@ -440,1523 +440,1523 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5893597630439735</v>
+        <v>0.6643415356573251</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5899863294600137</v>
+        <v>0.6619583048530417</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5893597630439735</v>
+        <v>0.6452813852813852</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5909261790840739</v>
+        <v>0.6489177489177489</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5928058783321941</v>
+        <v>0.6525541125541126</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5909876965140123</v>
+        <v>0.6418295739348371</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5909876965140123</v>
+        <v>0.6418295739348371</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5909876965140123</v>
+        <v>0.6400113921166553</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5909876965140123</v>
+        <v>0.632738664843928</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5909876965140123</v>
+        <v>0.6400729095465938</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5901093643198906</v>
+        <v>0.6351161995898837</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5904226475279106</v>
+        <v>0.6296616541353384</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5904226475279106</v>
+        <v>0.6296616541353384</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5901093643198906</v>
+        <v>0.6296616541353384</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5904226475279106</v>
+        <v>0.6353679653679654</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5894827979038505</v>
+        <v>0.6499134199134199</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.594937343358396</v>
+        <v>0.65053998632946</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.595250626566416</v>
+        <v>0.6514798359535201</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5955639097744361</v>
+        <v>0.6518546365914787</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5977568922305765</v>
+        <v>0.6518546365914787</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5977568922305765</v>
+        <v>0.6518546365914787</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6066575529733425</v>
+        <v>0.6518546365914787</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6108589655958077</v>
+        <v>0.6485315561631351</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6105456823877877</v>
+        <v>0.6485315561631351</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6105456823877877</v>
+        <v>0.6512280701754386</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6120505809979494</v>
+        <v>0.659440647072226</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6087275005696058</v>
+        <v>0.6576224652540442</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6067190704032809</v>
+        <v>0.6779357484620643</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6028309409888357</v>
+        <v>0.6982490316700842</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6056504898610162</v>
+        <v>0.6864000911369332</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6053372066529962</v>
+        <v>0.6867133743449533</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6089735702893597</v>
+        <v>0.7169958988380041</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6017008430166325</v>
+        <v>0.7169958988380041</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6001344269765322</v>
+        <v>0.7169958988380041</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5989428115743904</v>
+        <v>0.6763078149920255</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6022658920027341</v>
+        <v>0.690976304397357</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6072169059011164</v>
+        <v>0.690976304397357</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6093483709273183</v>
+        <v>0.690976304397357</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6093483709273183</v>
+        <v>0.701639325586694</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6093483709273183</v>
+        <v>0.6986295283663705</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6093483709273183</v>
+        <v>0.682265892002734</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6093483709273183</v>
+        <v>0.682265892002734</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6099749373433584</v>
+        <v>0.684084073820916</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6117931191615402</v>
+        <v>0.6868421052631579</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6117931191615402</v>
+        <v>0.6799441786283892</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6178127136021873</v>
+        <v>0.6799441786283892</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6178742310321257</v>
+        <v>0.6799441786283892</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6175609478241058</v>
+        <v>0.6645819093187515</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.638691045796309</v>
+        <v>0.6654602415128731</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6393176122123491</v>
+        <v>0.6654602415128731</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6393176122123491</v>
+        <v>0.7186295283663704</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6284700387331966</v>
+        <v>0.7173763955342902</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6227022100706311</v>
+        <v>0.7149931647300068</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5884700387331966</v>
+        <v>0.687781954887218</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5921064023695602</v>
+        <v>0.687781954887218</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.616246297562087</v>
+        <v>0.687781954887218</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6170631123262702</v>
+        <v>0.6729847345636819</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6170631123262702</v>
+        <v>0.6821371610845295</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.6253372066529961</v>
+        <v>0.6840168603326497</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6201959444064707</v>
+        <v>0.6934210526315789</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6201959444064707</v>
+        <v>0.6899749373433584</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.619004329004329</v>
+        <v>0.6899749373433584</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6228252449305081</v>
+        <v>0.6912280701754385</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.6267748917748918</v>
+        <v>0.6930462519936204</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.6267748917748918</v>
+        <v>0.6522294372294373</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.62558327637275</v>
+        <v>0.6525427204374573</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.62558327637275</v>
+        <v>0.6280280246069719</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.6634518113465482</v>
+        <v>0.6252084757347915</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.6634518113465482</v>
+        <v>0.6351777170198223</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.6634518113465482</v>
+        <v>0.6348029163818638</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.6474014581909319</v>
+        <v>0.5911665527455001</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6383105491000228</v>
+        <v>0.6107302346776031</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6383105491000228</v>
+        <v>0.5827022100706312</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6376839826839827</v>
+        <v>0.5827022100706312</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.6376839826839827</v>
+        <v>0.5739245841877421</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.6467748917748918</v>
+        <v>0.5739245841877421</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6467748917748918</v>
+        <v>0.5724196855775803</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6485930735930736</v>
+        <v>0.5724196855775803</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.6489063568010937</v>
+        <v>0.6036420596946912</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.64526999316473</v>
+        <v>0.5501594896331738</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6379972658920028</v>
+        <v>0.5704112554112555</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6270881749829118</v>
+        <v>0.56495670995671</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6957427660059239</v>
+        <v>0.5297846889952152</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.6957427660059239</v>
+        <v>0.5297846889952152</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.64495670995671</v>
+        <v>0.5288448393711551</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.6597539302802461</v>
+        <v>0.5288448393711551</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.6597539302802461</v>
+        <v>0.5104727728411939</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.6688448393711551</v>
+        <v>0.5104727728411939</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.6803189792663477</v>
+        <v>0.5125427204374573</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.6796924128503076</v>
+        <v>0.5045146958304854</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.6790658464342675</v>
+        <v>0.5018181818181818</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.6690966051492367</v>
+        <v>0.5018181818181818</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.6690966051492367</v>
+        <v>0.5018181818181818</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.6690966051492367</v>
+        <v>0.5036363636363637</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5689678742310321</v>
+        <v>0.5036363636363637</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5689678742310321</v>
+        <v>0.5018181818181818</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5910378218272955</v>
+        <v>0.5018181818181818</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.5883413078149921</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.590786056049214</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5638881294144452</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5844531784005469</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5941091364775575</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5753622693096377</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.679127363864206</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.6915413533834587</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.6915413533834587</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.6897231715652768</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.6667133743449534</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.667904989747095</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.6612588288904079</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.6667133743449534</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5638266119845068</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5638266119845068</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5547357028935976</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.508777625882889</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5069594440647073</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5033230804283436</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5015048986101618</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5015048986101618</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5015048986101618</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5015048986101618</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5015048986101618</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5015048986101618</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5015048986101618</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5051412622465254</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5051412622465254</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5051412622465254</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5051412622465254</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5051412622465254</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5051412622465254</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5051412622465254</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5051412622465254</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5124139895192527</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5139188881294144</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5154237867395762</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5208783321941217</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5208783321941217</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5208783321941217</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5223832308042834</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5205650489861016</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5223832308042834</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5223832308042834</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.525706311232627</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.525393028024607</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.525393028024607</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5069594440647073</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5069594440647073</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.508777625882889</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.508777625882889</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.508777625882889</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.508464342674869</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5102825244930508</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -1966,7 +1966,7 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -1976,7 +1976,7 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B156" t="n">
